--- a/StructureDefinition-PssResponseBundle.xlsx
+++ b/StructureDefinition-PssResponseBundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:33:36+00:00</t>
+    <t>2025-02-26T15:37:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
